--- a/report.xlsx
+++ b/report.xlsx
@@ -425,58 +425,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>user_story_id</t>
+          <t>Column_1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>Column_2</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Column_3</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
+          <t>Column_4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Generate EDI 270 Inquiry File</t>
+          <t>TC-EDI270-271-DEL-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>As a user, I want to generate a valid EDI 270 inquiry file so that eligibility requests can be processed successfully.</t>
+          <t>sample_edi270_valid_01.txt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -485,29 +475,358 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US-002</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Validate EDI 271 Response</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>As a user, I want to validate the EDI 271 response file so that delinquency status details are correctly received.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+          <t>Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>elements comply with the specification.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prepare valid</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Input data is prepared with correct formats and</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>trading partner identifiers.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sample_input_270.json</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Generate the 270 file using the</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>prepared input data.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The 270 file is generated with correct ISA/GS headers, ST/BHT segments,</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>and subscriber loops populated. The file contains no syntax errors.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>generated_270_01.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Validate the generated 270 file</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>against the ANSI X12 270 schema and implementation guide.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The 270 file passes schema validation with no missing mandatory</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>segments or invalid data elements.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>270_schema_validation_report.json</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC-EDI270-271-DEL-002</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sample_edi271_valid_01.txt</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Validate that the 271 response file generated for a member with delinquency status "Active - Pending Investigation" includes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>the EB segment in loop 2110C with EB01 set to "5" as per the business rule when the SBWM_EFF_DT is within 0-30 days. Confirm all other EB segment elements</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>remain unchanged and the file passes schema validation.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Valid 270 inquiry submitted for member with delinquency status active within 0-30 days.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Receive the 271 response file</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>corresponding to the 270 inquiry.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>271 file is received containing loop 2110C with EB segment having</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EB01 = "5".</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>generated_271_01.txt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Validate the 271 file against the</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ANSI X12 271 schema and implementation guide.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>271 file passes schema validation with required segments including ISA,</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GS, ST, BHT, HL, NM1, REF, DTP, and EB segments correctly populated.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>271_schema_validation_report.json</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
